--- a/PROCUREMENT/SpendLens_App/CFO_Report.xlsx
+++ b/PROCUREMENT/SpendLens_App/CFO_Report.xlsx
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="3">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
